--- a/tasks_gradebook_v3.xlsx
+++ b/tasks_gradebook_v3.xlsx
@@ -38,7 +38,7 @@
       <color rgb="00888888"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -85,11 +85,6 @@
         <fgColor rgb="00FFF9C4"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F0F0F0"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -117,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -150,9 +145,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -5085,11 +5077,11 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>فريق 1</t>
+          <t>فريق 6</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -5102,7 +5094,7 @@
         </is>
       </c>
       <c r="H42" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
@@ -5115,7 +5107,7 @@
         </is>
       </c>
       <c r="K42" s="3" t="n">
-        <v>76.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
@@ -5128,7 +5120,7 @@
         </is>
       </c>
       <c r="N42" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
@@ -5141,7 +5133,7 @@
         </is>
       </c>
       <c r="Q42" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
@@ -5157,17 +5149,17 @@
         <v>0</v>
       </c>
       <c r="U42" s="3" t="n">
-        <v>408</v>
+        <v>376.5</v>
       </c>
       <c r="V42" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W42" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
@@ -5194,15 +5186,15 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>فريق 1</t>
+          <t>فريق 3</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 16:38</t>
+          <t>2026-01-20 14:58</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -5211,11 +5203,11 @@
         </is>
       </c>
       <c r="H43" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 20:37</t>
+          <t>2026-02-04 11:17</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -5224,11 +5216,11 @@
         </is>
       </c>
       <c r="K43" s="3" t="n">
-        <v>76.2</v>
+        <v>86.8</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 22:45</t>
+          <t>2026-02-16 22:44</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
@@ -5237,11 +5229,11 @@
         </is>
       </c>
       <c r="N43" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 16:43</t>
+          <t>2026-03-04 09:07</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
@@ -5250,11 +5242,11 @@
         </is>
       </c>
       <c r="Q43" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:46</t>
+          <t>2026-03-20 16:46</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
@@ -5266,17 +5258,17 @@
         <v>0</v>
       </c>
       <c r="U43" s="3" t="n">
-        <v>408</v>
+        <v>392.7</v>
       </c>
       <c r="V43" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W43" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -5303,15 +5295,15 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>فريق 1</t>
+          <t>فريق 4</t>
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 16:38</t>
+          <t>2026-01-21 18:05</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -5324,7 +5316,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 20:37</t>
+          <t>2026-02-04 16:48</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -5333,11 +5325,11 @@
         </is>
       </c>
       <c r="K44" s="3" t="n">
-        <v>76.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 22:45</t>
+          <t>2026-02-17 15:49</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
@@ -5346,11 +5338,11 @@
         </is>
       </c>
       <c r="N44" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 16:43</t>
+          <t>2026-03-03 09:22</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
@@ -5359,11 +5351,11 @@
         </is>
       </c>
       <c r="Q44" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 17:46</t>
+          <t>2026-03-20 14:06</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
@@ -5375,17 +5367,17 @@
         <v>0</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>408</v>
+        <v>394.2</v>
       </c>
       <c r="V44" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W44" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
@@ -5412,11 +5404,11 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>فريق 1</t>
+          <t>فريق 6</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>80.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -5429,7 +5421,7 @@
         </is>
       </c>
       <c r="H45" s="3" t="n">
-        <v>81.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
@@ -5442,7 +5434,7 @@
         </is>
       </c>
       <c r="K45" s="3" t="n">
-        <v>76.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
@@ -5455,7 +5447,7 @@
         </is>
       </c>
       <c r="N45" s="3" t="n">
-        <v>83.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
@@ -5468,7 +5460,7 @@
         </is>
       </c>
       <c r="Q45" s="3" t="n">
-        <v>86.40000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
@@ -5484,17 +5476,17 @@
         <v>0</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>408</v>
+        <v>376.5</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>81.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -5521,7 +5513,7 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>فريق 2</t>
+          <t>فريق 5</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
@@ -5529,7 +5521,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 14:58</t>
+          <t>2026-01-20 14:02</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -5538,11 +5530,11 @@
         </is>
       </c>
       <c r="H46" s="3" t="n">
-        <v>85.5</v>
+        <v>71.3</v>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 11:17</t>
+          <t>2026-02-04 10:37</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -5551,11 +5543,11 @@
         </is>
       </c>
       <c r="K46" s="3" t="n">
-        <v>93.2</v>
+        <v>80.8</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 22:44</t>
+          <t>2026-02-18 15:00</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
@@ -5564,11 +5556,11 @@
         </is>
       </c>
       <c r="N46" s="3" t="n">
-        <v>83</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:07</t>
+          <t>2026-03-03 12:40</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
@@ -5577,11 +5569,11 @@
         </is>
       </c>
       <c r="Q46" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 16:46</t>
+          <t>2026-03-20 19:24</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
@@ -5593,17 +5585,17 @@
         <v>0</v>
       </c>
       <c r="U46" s="3" t="n">
-        <v>424.4</v>
+        <v>383.9</v>
       </c>
       <c r="V46" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W46" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
@@ -5630,15 +5622,15 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>فريق 2</t>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>75.8</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 14:58</t>
+          <t>2026-01-19 21:17</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -5647,11 +5639,11 @@
         </is>
       </c>
       <c r="H47" s="3" t="n">
-        <v>85.5</v>
+        <v>91</v>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 11:17</t>
+          <t>2026-02-05 15:23</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -5660,11 +5652,11 @@
         </is>
       </c>
       <c r="K47" s="3" t="n">
-        <v>93.2</v>
+        <v>83</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 22:44</t>
+          <t>2026-02-18 16:53</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
@@ -5673,11 +5665,11 @@
         </is>
       </c>
       <c r="N47" s="3" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:07</t>
+          <t>2026-03-05 18:05</t>
         </is>
       </c>
       <c r="P47" s="3" t="inlineStr">
@@ -5686,11 +5678,11 @@
         </is>
       </c>
       <c r="Q47" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 16:46</t>
+          <t>2026-03-20 15:43</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr">
@@ -5702,17 +5694,17 @@
         <v>0</v>
       </c>
       <c r="U47" s="3" t="n">
-        <v>424.4</v>
+        <v>432.1</v>
       </c>
       <c r="V47" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W47" s="3" t="n">
-        <v>84.90000000000001</v>
-      </c>
-      <c r="X47" s="3" t="inlineStr">
-        <is>
-          <t>B+</t>
+        <v>86.40000000000001</v>
+      </c>
+      <c r="X47" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y47" s="3" t="inlineStr">
@@ -5739,15 +5731,15 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>فريق 2</t>
+          <t>فريق 4</t>
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>75.8</v>
+        <v>74.2</v>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 14:58</t>
+          <t>2026-01-21 18:05</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -5756,11 +5748,11 @@
         </is>
       </c>
       <c r="H48" s="3" t="n">
-        <v>85.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 11:17</t>
+          <t>2026-02-04 16:48</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -5769,11 +5761,11 @@
         </is>
       </c>
       <c r="K48" s="3" t="n">
-        <v>93.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 22:44</t>
+          <t>2026-02-17 15:49</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -5782,11 +5774,11 @@
         </is>
       </c>
       <c r="N48" s="3" t="n">
-        <v>83</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:07</t>
+          <t>2026-03-03 09:22</t>
         </is>
       </c>
       <c r="P48" s="3" t="inlineStr">
@@ -5795,11 +5787,11 @@
         </is>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 16:46</t>
+          <t>2026-03-20 14:06</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr">
@@ -5811,17 +5803,17 @@
         <v>0</v>
       </c>
       <c r="U48" s="3" t="n">
-        <v>424.4</v>
+        <v>394.2</v>
       </c>
       <c r="V48" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W48" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="X48" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y48" s="3" t="inlineStr">
@@ -5848,7 +5840,7 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>فريق 2</t>
+          <t>فريق 5</t>
         </is>
       </c>
       <c r="E49" s="3" t="n">
@@ -5856,7 +5848,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20 14:58</t>
+          <t>2026-01-20 14:02</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -5865,11 +5857,11 @@
         </is>
       </c>
       <c r="H49" s="3" t="n">
-        <v>85.5</v>
+        <v>71.3</v>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 11:17</t>
+          <t>2026-02-04 10:37</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -5878,11 +5870,11 @@
         </is>
       </c>
       <c r="K49" s="3" t="n">
-        <v>93.2</v>
+        <v>80.8</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>2026-02-16 22:44</t>
+          <t>2026-02-18 15:00</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
@@ -5891,11 +5883,11 @@
         </is>
       </c>
       <c r="N49" s="3" t="n">
-        <v>83</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:07</t>
+          <t>2026-03-03 12:40</t>
         </is>
       </c>
       <c r="P49" s="3" t="inlineStr">
@@ -5904,11 +5896,11 @@
         </is>
       </c>
       <c r="Q49" s="3" t="n">
-        <v>86.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 16:46</t>
+          <t>2026-03-20 19:24</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr">
@@ -5920,17 +5912,17 @@
         <v>0</v>
       </c>
       <c r="U49" s="3" t="n">
-        <v>424.4</v>
+        <v>383.9</v>
       </c>
       <c r="V49" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W49" s="3" t="n">
-        <v>84.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="X49" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y49" s="3" t="inlineStr">
@@ -5957,15 +5949,15 @@
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 6</t>
         </is>
       </c>
       <c r="E50" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 18:05</t>
+          <t>2026-01-21 16:38</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -5974,11 +5966,11 @@
         </is>
       </c>
       <c r="H50" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 16:48</t>
+          <t>2026-02-05 20:37</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -5987,11 +5979,11 @@
         </is>
       </c>
       <c r="K50" s="3" t="n">
-        <v>78</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:49</t>
+          <t>2026-02-16 22:45</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -6000,11 +5992,11 @@
         </is>
       </c>
       <c r="N50" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:22</t>
+          <t>2026-03-03 16:43</t>
         </is>
       </c>
       <c r="P50" s="3" t="inlineStr">
@@ -6013,11 +6005,11 @@
         </is>
       </c>
       <c r="Q50" s="3" t="n">
-        <v>84</v>
+        <v>80.2</v>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 14:06</t>
+          <t>2026-03-19 17:46</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr">
@@ -6029,13 +6021,13 @@
         <v>0</v>
       </c>
       <c r="U50" s="3" t="n">
-        <v>382.4</v>
+        <v>376.5</v>
       </c>
       <c r="V50" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W50" s="3" t="n">
-        <v>76.5</v>
+        <v>75.3</v>
       </c>
       <c r="X50" s="3" t="inlineStr">
         <is>
@@ -6066,11 +6058,11 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 4</t>
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -6083,7 +6075,7 @@
         </is>
       </c>
       <c r="H51" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
@@ -6096,7 +6088,7 @@
         </is>
       </c>
       <c r="K51" s="3" t="n">
-        <v>78</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
@@ -6109,7 +6101,7 @@
         </is>
       </c>
       <c r="N51" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
@@ -6122,7 +6114,7 @@
         </is>
       </c>
       <c r="Q51" s="3" t="n">
-        <v>84</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
@@ -6138,13 +6130,13 @@
         <v>0</v>
       </c>
       <c r="U51" s="3" t="n">
-        <v>382.4</v>
+        <v>394.2</v>
       </c>
       <c r="V51" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W51" s="3" t="n">
-        <v>76.5</v>
+        <v>78.8</v>
       </c>
       <c r="X51" s="3" t="inlineStr">
         <is>
@@ -6175,15 +6167,15 @@
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 2</t>
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 18:05</t>
+          <t>2026-01-19 11:59</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -6192,11 +6184,11 @@
         </is>
       </c>
       <c r="H52" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 16:48</t>
+          <t>2026-02-04 19:35</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -6205,11 +6197,11 @@
         </is>
       </c>
       <c r="K52" s="3" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:49</t>
+          <t>2026-02-17 15:54</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -6218,11 +6210,11 @@
         </is>
       </c>
       <c r="N52" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:22</t>
+          <t>2026-03-02 13:08</t>
         </is>
       </c>
       <c r="P52" s="3" t="inlineStr">
@@ -6231,11 +6223,11 @@
         </is>
       </c>
       <c r="Q52" s="3" t="n">
-        <v>84</v>
+        <v>84.5</v>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 14:06</t>
+          <t>2026-03-20 10:04</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr">
@@ -6247,17 +6239,17 @@
         <v>0</v>
       </c>
       <c r="U52" s="3" t="n">
-        <v>382.4</v>
+        <v>411.4</v>
       </c>
       <c r="V52" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W52" s="3" t="n">
-        <v>76.5</v>
+        <v>82.3</v>
       </c>
       <c r="X52" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y52" s="3" t="inlineStr">
@@ -6284,15 +6276,15 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 2</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>70.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21 18:05</t>
+          <t>2026-01-19 11:59</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -6301,11 +6293,11 @@
         </is>
       </c>
       <c r="H53" s="3" t="n">
-        <v>77.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 16:48</t>
+          <t>2026-02-04 19:35</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -6314,11 +6306,11 @@
         </is>
       </c>
       <c r="K53" s="3" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:49</t>
+          <t>2026-02-17 15:54</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -6327,11 +6319,11 @@
         </is>
       </c>
       <c r="N53" s="3" t="n">
-        <v>72.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 09:22</t>
+          <t>2026-03-02 13:08</t>
         </is>
       </c>
       <c r="P53" s="3" t="inlineStr">
@@ -6340,11 +6332,11 @@
         </is>
       </c>
       <c r="Q53" s="3" t="n">
-        <v>84</v>
+        <v>84.5</v>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 14:06</t>
+          <t>2026-03-20 10:04</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr">
@@ -6356,17 +6348,17 @@
         <v>0</v>
       </c>
       <c r="U53" s="3" t="n">
-        <v>382.4</v>
+        <v>411.4</v>
       </c>
       <c r="V53" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W53" s="3" t="n">
-        <v>76.5</v>
+        <v>82.3</v>
       </c>
       <c r="X53" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y53" s="3" t="inlineStr">
@@ -6393,15 +6385,15 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>فريق 4</t>
+          <t>فريق 3</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>81.5</v>
+        <v>69.5</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 14:02</t>
+          <t>2026-01-20 14:58</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -6410,11 +6402,11 @@
         </is>
       </c>
       <c r="H54" s="3" t="n">
-        <v>77.3</v>
+        <v>79.2</v>
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 10:37</t>
+          <t>2026-02-04 11:17</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -6423,11 +6415,11 @@
         </is>
       </c>
       <c r="K54" s="3" t="n">
-        <v>87.3</v>
+        <v>86.8</v>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:00</t>
+          <t>2026-02-16 22:44</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -6436,11 +6428,11 @@
         </is>
       </c>
       <c r="N54" s="3" t="n">
-        <v>84.7</v>
+        <v>76.7</v>
       </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 12:40</t>
+          <t>2026-03-04 09:07</t>
         </is>
       </c>
       <c r="P54" s="3" t="inlineStr">
@@ -6449,11 +6441,11 @@
         </is>
       </c>
       <c r="Q54" s="3" t="n">
-        <v>85.3</v>
+        <v>80.5</v>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 19:24</t>
+          <t>2026-03-20 16:46</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr">
@@ -6465,17 +6457,17 @@
         <v>0</v>
       </c>
       <c r="U54" s="3" t="n">
-        <v>416.1</v>
+        <v>392.7</v>
       </c>
       <c r="V54" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W54" s="3" t="n">
-        <v>83.2</v>
+        <v>78.5</v>
       </c>
       <c r="X54" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y54" s="3" t="inlineStr">
@@ -6502,15 +6494,15 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>فريق 4</t>
+          <t>فريق 2</t>
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>81.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 14:02</t>
+          <t>2026-01-19 11:59</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -6519,11 +6511,11 @@
         </is>
       </c>
       <c r="H55" s="3" t="n">
-        <v>77.3</v>
+        <v>86.2</v>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 10:37</t>
+          <t>2026-02-04 19:35</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -6532,11 +6524,11 @@
         </is>
       </c>
       <c r="K55" s="3" t="n">
-        <v>87.3</v>
+        <v>81</v>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:00</t>
+          <t>2026-02-17 15:54</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
@@ -6545,11 +6537,11 @@
         </is>
       </c>
       <c r="N55" s="3" t="n">
-        <v>84.7</v>
+        <v>81.3</v>
       </c>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 12:40</t>
+          <t>2026-03-02 13:08</t>
         </is>
       </c>
       <c r="P55" s="3" t="inlineStr">
@@ -6558,11 +6550,11 @@
         </is>
       </c>
       <c r="Q55" s="3" t="n">
-        <v>85.3</v>
+        <v>84.5</v>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 19:24</t>
+          <t>2026-03-20 10:04</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr">
@@ -6574,13 +6566,13 @@
         <v>0</v>
       </c>
       <c r="U55" s="3" t="n">
-        <v>416.1</v>
+        <v>411.4</v>
       </c>
       <c r="V55" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W55" s="3" t="n">
-        <v>83.2</v>
+        <v>82.3</v>
       </c>
       <c r="X55" s="3" t="inlineStr">
         <is>
@@ -6611,15 +6603,15 @@
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>فريق 4</t>
+          <t>فريق 3</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>81.5</v>
+        <v>69.5</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 14:02</t>
+          <t>2026-01-20 14:58</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -6628,11 +6620,11 @@
         </is>
       </c>
       <c r="H56" s="3" t="n">
-        <v>77.3</v>
+        <v>79.2</v>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 10:37</t>
+          <t>2026-02-04 11:17</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -6641,11 +6633,11 @@
         </is>
       </c>
       <c r="K56" s="3" t="n">
-        <v>87.3</v>
+        <v>86.8</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:00</t>
+          <t>2026-02-16 22:44</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
@@ -6654,11 +6646,11 @@
         </is>
       </c>
       <c r="N56" s="3" t="n">
-        <v>84.7</v>
+        <v>76.7</v>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 12:40</t>
+          <t>2026-03-04 09:07</t>
         </is>
       </c>
       <c r="P56" s="3" t="inlineStr">
@@ -6667,11 +6659,11 @@
         </is>
       </c>
       <c r="Q56" s="3" t="n">
-        <v>85.3</v>
+        <v>80.5</v>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 19:24</t>
+          <t>2026-03-20 16:46</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr">
@@ -6683,17 +6675,17 @@
         <v>0</v>
       </c>
       <c r="U56" s="3" t="n">
-        <v>416.1</v>
+        <v>392.7</v>
       </c>
       <c r="V56" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W56" s="3" t="n">
-        <v>83.2</v>
+        <v>78.5</v>
       </c>
       <c r="X56" s="3" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y56" s="3" t="inlineStr">
@@ -6720,15 +6712,15 @@
       </c>
       <c r="D57" s="8" t="inlineStr">
         <is>
-          <t>فريق 4</t>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>81.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 14:02</t>
+          <t>2026-01-19 21:17</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -6737,11 +6729,11 @@
         </is>
       </c>
       <c r="H57" s="3" t="n">
-        <v>77.3</v>
+        <v>91</v>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04 10:37</t>
+          <t>2026-02-05 15:23</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -6750,11 +6742,11 @@
         </is>
       </c>
       <c r="K57" s="3" t="n">
-        <v>87.3</v>
+        <v>83</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>2026-02-17 15:00</t>
+          <t>2026-02-18 16:53</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
@@ -6763,11 +6755,11 @@
         </is>
       </c>
       <c r="N57" s="3" t="n">
-        <v>84.7</v>
+        <v>79</v>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03 12:40</t>
+          <t>2026-03-05 18:05</t>
         </is>
       </c>
       <c r="P57" s="3" t="inlineStr">
@@ -6776,11 +6768,11 @@
         </is>
       </c>
       <c r="Q57" s="3" t="n">
-        <v>85.3</v>
+        <v>96.7</v>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 19:24</t>
+          <t>2026-03-20 15:43</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr">
@@ -6792,17 +6784,17 @@
         <v>0</v>
       </c>
       <c r="U57" s="3" t="n">
-        <v>416.1</v>
+        <v>432.1</v>
       </c>
       <c r="V57" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W57" s="3" t="n">
-        <v>83.2</v>
-      </c>
-      <c r="X57" s="3" t="inlineStr">
-        <is>
-          <t>B+</t>
+        <v>86.40000000000001</v>
+      </c>
+      <c r="X57" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y57" s="3" t="inlineStr">
@@ -6829,15 +6821,15 @@
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>فريق 5</t>
+          <t>فريق 3</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>74</v>
+        <v>69.5</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 21:17</t>
+          <t>2026-01-20 14:58</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -6846,11 +6838,11 @@
         </is>
       </c>
       <c r="H58" s="3" t="n">
-        <v>83.5</v>
+        <v>79.2</v>
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 15:23</t>
+          <t>2026-02-04 11:17</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -6859,11 +6851,11 @@
         </is>
       </c>
       <c r="K58" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 16:53</t>
+          <t>2026-02-16 22:44</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -6872,11 +6864,11 @@
         </is>
       </c>
       <c r="N58" s="3" t="n">
-        <v>73.3</v>
+        <v>76.7</v>
       </c>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 18:05</t>
+          <t>2026-03-04 09:07</t>
         </is>
       </c>
       <c r="P58" s="3" t="inlineStr">
@@ -6885,11 +6877,11 @@
         </is>
       </c>
       <c r="Q58" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 15:43</t>
+          <t>2026-03-20 16:46</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr">
@@ -6901,13 +6893,13 @@
         <v>0</v>
       </c>
       <c r="U58" s="3" t="n">
-        <v>399.1</v>
+        <v>392.7</v>
       </c>
       <c r="V58" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W58" s="3" t="n">
-        <v>79.8</v>
+        <v>78.5</v>
       </c>
       <c r="X58" s="3" t="inlineStr">
         <is>
@@ -6938,15 +6930,15 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>فريق 5</t>
+          <t>فريق 2</t>
         </is>
       </c>
       <c r="E59" s="3" t="n">
-        <v>74</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 21:17</t>
+          <t>2026-01-19 11:59</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -6955,11 +6947,11 @@
         </is>
       </c>
       <c r="H59" s="3" t="n">
-        <v>83.5</v>
+        <v>86.2</v>
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 15:23</t>
+          <t>2026-02-04 19:35</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -6968,11 +6960,11 @@
         </is>
       </c>
       <c r="K59" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>81</v>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 16:53</t>
+          <t>2026-02-17 15:54</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -6981,11 +6973,11 @@
         </is>
       </c>
       <c r="N59" s="3" t="n">
-        <v>73.3</v>
+        <v>81.3</v>
       </c>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 18:05</t>
+          <t>2026-03-02 13:08</t>
         </is>
       </c>
       <c r="P59" s="3" t="inlineStr">
@@ -6994,11 +6986,11 @@
         </is>
       </c>
       <c r="Q59" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 15:43</t>
+          <t>2026-03-20 10:04</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr">
@@ -7010,17 +7002,17 @@
         <v>0</v>
       </c>
       <c r="U59" s="3" t="n">
-        <v>399.1</v>
+        <v>411.4</v>
       </c>
       <c r="V59" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W59" s="3" t="n">
-        <v>79.8</v>
+        <v>82.3</v>
       </c>
       <c r="X59" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="Y59" s="3" t="inlineStr">
@@ -7047,11 +7039,11 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>فريق 5</t>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>74</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -7064,7 +7056,7 @@
         </is>
       </c>
       <c r="H60" s="3" t="n">
-        <v>83.5</v>
+        <v>91</v>
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
@@ -7077,7 +7069,7 @@
         </is>
       </c>
       <c r="K60" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
@@ -7090,11 +7082,11 @@
         </is>
       </c>
       <c r="N60" s="3" t="n">
-        <v>73.3</v>
+        <v>79</v>
       </c>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 18:05</t>
+          <t>2026-03-05 18:05</t>
         </is>
       </c>
       <c r="P60" s="3" t="inlineStr">
@@ -7103,7 +7095,7 @@
         </is>
       </c>
       <c r="Q60" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
@@ -7119,17 +7111,17 @@
         <v>0</v>
       </c>
       <c r="U60" s="3" t="n">
-        <v>399.1</v>
+        <v>432.1</v>
       </c>
       <c r="V60" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W60" s="3" t="n">
-        <v>79.8</v>
-      </c>
-      <c r="X60" s="3" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>86.40000000000001</v>
+      </c>
+      <c r="X60" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="Y60" s="3" t="inlineStr">
@@ -7160,11 +7152,11 @@
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>74</v>
+        <v>75.8</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19 21:17</t>
+          <t>2026-01-20 14:02</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -7173,11 +7165,11 @@
         </is>
       </c>
       <c r="H61" s="3" t="n">
-        <v>83.5</v>
+        <v>71.3</v>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 15:23</t>
+          <t>2026-02-04 10:37</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -7186,11 +7178,11 @@
         </is>
       </c>
       <c r="K61" s="3" t="n">
-        <v>76.40000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 16:53</t>
+          <t>2026-02-18 15:00</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
@@ -7199,11 +7191,11 @@
         </is>
       </c>
       <c r="N61" s="3" t="n">
-        <v>73.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04 18:05</t>
+          <t>2026-03-03 12:40</t>
         </is>
       </c>
       <c r="P61" s="3" t="inlineStr">
@@ -7212,11 +7204,11 @@
         </is>
       </c>
       <c r="Q61" s="3" t="n">
-        <v>91.90000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20 15:43</t>
+          <t>2026-03-20 19:24</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr">
@@ -7228,13 +7220,13 @@
         <v>0</v>
       </c>
       <c r="U61" s="3" t="n">
-        <v>399.1</v>
+        <v>383.9</v>
       </c>
       <c r="V61" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W61" s="3" t="n">
-        <v>79.8</v>
+        <v>76.8</v>
       </c>
       <c r="X61" s="3" t="inlineStr">
         <is>
@@ -7265,28 +7257,28 @@
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>فريق 1</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 19:18</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+          <t>فريق 6</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-22 13:26</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="H62" s="3" t="n">
-        <v>78.8</v>
+        <v>66.7</v>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 14:00</t>
+          <t>2026-02-06 05:40</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -7295,11 +7287,11 @@
         </is>
       </c>
       <c r="K62" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 19:34</t>
+          <t>2026-02-20 04:46</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
@@ -7308,11 +7300,11 @@
         </is>
       </c>
       <c r="N62" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 23:17</t>
+          <t>2026-03-05 07:48</t>
         </is>
       </c>
       <c r="P62" s="3" t="inlineStr">
@@ -7320,34 +7312,34 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-21 01:36</t>
-        </is>
-      </c>
-      <c r="S62" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q62" s="3" t="n">
+        <v>74.09999999999999</v>
+      </c>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19 17:51</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T62" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U62" s="3" t="n">
-        <v>343.7</v>
+        <v>357</v>
       </c>
       <c r="V62" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W62" s="3" t="n">
-        <v>68.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="X62" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y62" s="3" t="inlineStr">
@@ -7374,15 +7366,15 @@
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>فريق 1</t>
+          <t>فريق 4</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
-        <v>55.7</v>
+        <v>45.1</v>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>2026-01-23 19:18</t>
+          <t>2026-01-24 01:48</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">
@@ -7391,11 +7383,11 @@
         </is>
       </c>
       <c r="H63" s="3" t="n">
-        <v>78.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 14:00</t>
+          <t>2026-02-05 23:24</t>
         </is>
       </c>
       <c r="J63" s="3" t="inlineStr">
@@ -7403,38 +7395,38 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K63" s="3" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="L63" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-18 19:34</t>
-        </is>
-      </c>
-      <c r="M63" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="N63" s="3" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 23:17</t>
-        </is>
-      </c>
-      <c r="P63" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="K63" s="6" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="L63" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20 19:00</t>
+        </is>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="N63" s="6" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="O63" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 00:24</t>
+        </is>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="Q63" s="6" t="n">
-        <v>56.4</v>
+        <v>58.1</v>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>2026-03-21 01:36</t>
+          <t>2026-03-21 00:24</t>
         </is>
       </c>
       <c r="S63" s="6" t="inlineStr">
@@ -7446,17 +7438,17 @@
         <v>0</v>
       </c>
       <c r="U63" s="3" t="n">
-        <v>343.7</v>
+        <v>263.9</v>
       </c>
       <c r="V63" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W63" s="3" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="X63" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>52.8</v>
+      </c>
+      <c r="X63" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y63" s="3" t="inlineStr">
@@ -7483,89 +7475,89 @@
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>فريق 1</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 19:18</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
+          <t>فريق 2</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-22 13:31</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05 19:07</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-19 07:08</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="N64" s="6" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="O64" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-06 19:12</t>
+        </is>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H64" s="3" t="n">
-        <v>78.8</v>
-      </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-05 14:00</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="n">
-        <v>78.90000000000001</v>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-18 19:34</t>
-        </is>
-      </c>
-      <c r="M64" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="N64" s="3" t="n">
-        <v>73.90000000000001</v>
-      </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 23:17</t>
-        </is>
-      </c>
-      <c r="P64" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-21 01:36</t>
-        </is>
-      </c>
-      <c r="S64" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q64" s="3" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-20 15:10</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T64" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U64" s="3" t="n">
-        <v>343.7</v>
+        <v>371</v>
       </c>
       <c r="V64" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W64" s="3" t="n">
-        <v>68.7</v>
+        <v>74.2</v>
       </c>
       <c r="X64" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y64" s="3" t="inlineStr">
@@ -7595,25 +7587,25 @@
           <t>فريق 1</t>
         </is>
       </c>
-      <c r="E65" s="6" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-23 19:18</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="E65" s="3" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-22 05:09</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="H65" s="3" t="n">
-        <v>78.8</v>
+        <v>70.2</v>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 14:00</t>
+          <t>2026-02-06 01:24</t>
         </is>
       </c>
       <c r="J65" s="3" t="inlineStr">
@@ -7622,11 +7614,11 @@
         </is>
       </c>
       <c r="K65" s="3" t="n">
-        <v>78.90000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="L65" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18 19:34</t>
+          <t>2026-02-20 00:45</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
@@ -7635,11 +7627,11 @@
         </is>
       </c>
       <c r="N65" s="3" t="n">
-        <v>73.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 23:17</t>
+          <t>2026-03-05 10:03</t>
         </is>
       </c>
       <c r="P65" s="3" t="inlineStr">
@@ -7647,34 +7639,34 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q65" s="6" t="n">
-        <v>56.4</v>
-      </c>
-      <c r="R65" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-21 01:36</t>
-        </is>
-      </c>
-      <c r="S65" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q65" s="3" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19 17:51</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T65" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U65" s="3" t="n">
-        <v>343.7</v>
+        <v>388.4</v>
       </c>
       <c r="V65" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W65" s="3" t="n">
-        <v>68.7</v>
+        <v>77.7</v>
       </c>
       <c r="X65" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y65" s="3" t="inlineStr">
@@ -7701,15 +7693,15 @@
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>فريق 2</t>
+          <t>فريق 5</t>
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>73.7</v>
+        <v>75.7</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 15:15</t>
+          <t>2026-01-23 07:28</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -7718,11 +7710,11 @@
         </is>
       </c>
       <c r="H66" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 07:30</t>
+          <t>2026-02-05 22:12</t>
         </is>
       </c>
       <c r="J66" s="3" t="inlineStr">
@@ -7731,11 +7723,11 @@
         </is>
       </c>
       <c r="K66" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="L66" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 06:36</t>
+          <t>2026-02-19 09:58</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
@@ -7744,11 +7736,11 @@
         </is>
       </c>
       <c r="N66" s="3" t="n">
-        <v>69.7</v>
+        <v>71.8</v>
       </c>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 09:37</t>
+          <t>2026-03-06 20:03</t>
         </is>
       </c>
       <c r="P66" s="3" t="inlineStr">
@@ -7757,11 +7749,11 @@
         </is>
       </c>
       <c r="Q66" s="3" t="n">
-        <v>74.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 19:40</t>
+          <t>2026-03-20 12:12</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr">
@@ -7773,17 +7765,17 @@
         <v>0</v>
       </c>
       <c r="U66" s="3" t="n">
-        <v>367.1</v>
+        <v>380.6</v>
       </c>
       <c r="V66" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W66" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="X66" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y66" s="3" t="inlineStr">
@@ -7810,15 +7802,15 @@
       </c>
       <c r="D67" s="9" t="inlineStr">
         <is>
-          <t>فريق 2</t>
+          <t>فريق 6</t>
         </is>
       </c>
       <c r="E67" s="3" t="n">
-        <v>73.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 15:15</t>
+          <t>2026-01-22 13:26</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -7827,11 +7819,11 @@
         </is>
       </c>
       <c r="H67" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 07:30</t>
+          <t>2026-02-06 05:40</t>
         </is>
       </c>
       <c r="J67" s="3" t="inlineStr">
@@ -7840,11 +7832,11 @@
         </is>
       </c>
       <c r="K67" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="L67" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 06:36</t>
+          <t>2026-02-20 04:46</t>
         </is>
       </c>
       <c r="M67" s="3" t="inlineStr">
@@ -7853,11 +7845,11 @@
         </is>
       </c>
       <c r="N67" s="3" t="n">
-        <v>69.7</v>
+        <v>68.5</v>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 09:37</t>
+          <t>2026-03-05 07:48</t>
         </is>
       </c>
       <c r="P67" s="3" t="inlineStr">
@@ -7866,11 +7858,11 @@
         </is>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>74.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 19:40</t>
+          <t>2026-03-19 17:51</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr">
@@ -7882,13 +7874,13 @@
         <v>0</v>
       </c>
       <c r="U67" s="3" t="n">
-        <v>367.1</v>
+        <v>357</v>
       </c>
       <c r="V67" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W67" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="X67" s="3" t="inlineStr">
         <is>
@@ -7919,28 +7911,28 @@
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>فريق 2</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>73.7</v>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 15:15</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 4</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-24 01:48</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H68" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 07:30</t>
+          <t>2026-02-05 23:24</t>
         </is>
       </c>
       <c r="J68" s="3" t="inlineStr">
@@ -7948,60 +7940,60 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K68" s="3" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="L68" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 06:36</t>
-        </is>
-      </c>
-      <c r="M68" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="N68" s="3" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 09:37</t>
-        </is>
-      </c>
-      <c r="P68" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="Q68" s="3" t="n">
-        <v>74.5</v>
-      </c>
-      <c r="R68" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-19 19:40</t>
-        </is>
-      </c>
-      <c r="S68" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="K68" s="6" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="L68" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20 19:00</t>
+        </is>
+      </c>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="N68" s="6" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="O68" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 00:24</t>
+        </is>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="n">
+        <v>58.1</v>
+      </c>
+      <c r="R68" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-21 00:24</t>
+        </is>
+      </c>
+      <c r="S68" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="T68" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U68" s="3" t="n">
-        <v>367.1</v>
+        <v>263.9</v>
       </c>
       <c r="V68" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W68" s="3" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="X68" s="3" t="inlineStr">
-        <is>
-          <t>C+</t>
+        <v>52.8</v>
+      </c>
+      <c r="X68" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y68" s="3" t="inlineStr">
@@ -8028,15 +8020,15 @@
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>فريق 2</t>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E69" s="3" t="n">
-        <v>73.7</v>
+        <v>74.8</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 15:15</t>
+          <t>2026-01-22 05:09</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -8045,11 +8037,11 @@
         </is>
       </c>
       <c r="H69" s="3" t="n">
-        <v>69.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="I69" s="3" t="inlineStr">
         <is>
-          <t>2026-02-06 07:30</t>
+          <t>2026-02-06 01:24</t>
         </is>
       </c>
       <c r="J69" s="3" t="inlineStr">
@@ -8058,11 +8050,11 @@
         </is>
       </c>
       <c r="K69" s="3" t="n">
-        <v>79.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="L69" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 06:36</t>
+          <t>2026-02-20 00:45</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
@@ -8071,11 +8063,11 @@
         </is>
       </c>
       <c r="N69" s="3" t="n">
-        <v>69.7</v>
+        <v>86.7</v>
       </c>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 09:37</t>
+          <t>2026-03-05 10:03</t>
         </is>
       </c>
       <c r="P69" s="3" t="inlineStr">
@@ -8084,11 +8076,11 @@
         </is>
       </c>
       <c r="Q69" s="3" t="n">
-        <v>74.5</v>
+        <v>79.5</v>
       </c>
       <c r="R69" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 19:40</t>
+          <t>2026-03-19 17:51</t>
         </is>
       </c>
       <c r="S69" s="3" t="inlineStr">
@@ -8100,17 +8092,17 @@
         <v>0</v>
       </c>
       <c r="U69" s="3" t="n">
-        <v>367.1</v>
+        <v>388.4</v>
       </c>
       <c r="V69" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W69" s="3" t="n">
-        <v>73.40000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="X69" s="3" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y69" s="3" t="inlineStr">
@@ -8137,15 +8129,15 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 6</t>
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>61.1</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 15:39</t>
+          <t>2026-01-22 13:26</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -8154,11 +8146,11 @@
         </is>
       </c>
       <c r="H70" s="3" t="n">
-        <v>74.8</v>
+        <v>66.7</v>
       </c>
       <c r="I70" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 05:49</t>
+          <t>2026-02-06 05:40</t>
         </is>
       </c>
       <c r="J70" s="3" t="inlineStr">
@@ -8167,11 +8159,11 @@
         </is>
       </c>
       <c r="K70" s="3" t="n">
-        <v>70.7</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="L70" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 07:44</t>
+          <t>2026-02-20 04:46</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
@@ -8179,25 +8171,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N70" s="6" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="O70" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 21:12</t>
-        </is>
-      </c>
-      <c r="P70" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N70" s="3" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-05 07:48</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>82.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="R70" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 01:28</t>
+          <t>2026-03-19 17:51</t>
         </is>
       </c>
       <c r="S70" s="3" t="inlineStr">
@@ -8209,17 +8201,17 @@
         <v>0</v>
       </c>
       <c r="U70" s="3" t="n">
-        <v>344.7</v>
+        <v>357</v>
       </c>
       <c r="V70" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W70" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="X70" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y70" s="3" t="inlineStr">
@@ -8246,15 +8238,15 @@
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E71" s="3" t="n">
-        <v>61.1</v>
+        <v>74.8</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 15:39</t>
+          <t>2026-01-22 05:09</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -8263,11 +8255,11 @@
         </is>
       </c>
       <c r="H71" s="3" t="n">
-        <v>74.8</v>
+        <v>70.2</v>
       </c>
       <c r="I71" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 05:49</t>
+          <t>2026-02-06 01:24</t>
         </is>
       </c>
       <c r="J71" s="3" t="inlineStr">
@@ -8276,11 +8268,11 @@
         </is>
       </c>
       <c r="K71" s="3" t="n">
-        <v>70.7</v>
+        <v>77.2</v>
       </c>
       <c r="L71" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 07:44</t>
+          <t>2026-02-20 00:45</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
@@ -8288,25 +8280,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N71" s="6" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="O71" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 21:12</t>
-        </is>
-      </c>
-      <c r="P71" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N71" s="3" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-05 10:03</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>82.3</v>
+        <v>79.5</v>
       </c>
       <c r="R71" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 01:28</t>
+          <t>2026-03-19 17:51</t>
         </is>
       </c>
       <c r="S71" s="3" t="inlineStr">
@@ -8318,17 +8310,17 @@
         <v>0</v>
       </c>
       <c r="U71" s="3" t="n">
-        <v>344.7</v>
+        <v>388.4</v>
       </c>
       <c r="V71" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W71" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>77.7</v>
       </c>
       <c r="X71" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y71" s="3" t="inlineStr">
@@ -8355,15 +8347,15 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>فريق 3</t>
+          <t>فريق 5</t>
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>61.1</v>
+        <v>75.7</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 15:39</t>
+          <t>2026-01-23 07:28</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -8372,11 +8364,11 @@
         </is>
       </c>
       <c r="H72" s="3" t="n">
-        <v>74.8</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I72" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 05:49</t>
+          <t>2026-02-05 22:12</t>
         </is>
       </c>
       <c r="J72" s="3" t="inlineStr">
@@ -8385,11 +8377,11 @@
         </is>
       </c>
       <c r="K72" s="3" t="n">
-        <v>70.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="L72" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 07:44</t>
+          <t>2026-02-19 09:58</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
@@ -8397,25 +8389,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N72" s="6" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="O72" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 21:12</t>
-        </is>
-      </c>
-      <c r="P72" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N72" s="3" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-06 20:03</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q72" s="3" t="n">
-        <v>82.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="R72" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 01:28</t>
+          <t>2026-03-20 12:12</t>
         </is>
       </c>
       <c r="S72" s="3" t="inlineStr">
@@ -8427,17 +8419,17 @@
         <v>0</v>
       </c>
       <c r="U72" s="3" t="n">
-        <v>344.7</v>
+        <v>380.6</v>
       </c>
       <c r="V72" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W72" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="X72" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y72" s="3" t="inlineStr">
@@ -8467,25 +8459,25 @@
           <t>فريق 3</t>
         </is>
       </c>
-      <c r="E73" s="3" t="n">
-        <v>61.1</v>
-      </c>
-      <c r="F73" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 15:39</t>
-        </is>
-      </c>
-      <c r="G73" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="E73" s="6" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-24 01:48</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H73" s="3" t="n">
-        <v>74.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I73" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 05:49</t>
+          <t>2026-02-05 13:19</t>
         </is>
       </c>
       <c r="J73" s="3" t="inlineStr">
@@ -8494,11 +8486,11 @@
         </is>
       </c>
       <c r="K73" s="3" t="n">
-        <v>70.7</v>
+        <v>67.8</v>
       </c>
       <c r="L73" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 07:44</t>
+          <t>2026-02-19 14:31</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
@@ -8506,25 +8498,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N73" s="6" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="O73" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-06 21:12</t>
-        </is>
-      </c>
-      <c r="P73" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="N73" s="3" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-05 08:19</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="Q73" s="3" t="n">
-        <v>82.3</v>
+        <v>78.7</v>
       </c>
       <c r="R73" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 01:28</t>
+          <t>2026-03-19 08:02</t>
         </is>
       </c>
       <c r="S73" s="3" t="inlineStr">
@@ -8536,13 +8528,13 @@
         <v>0</v>
       </c>
       <c r="U73" s="3" t="n">
-        <v>344.7</v>
+        <v>339.2</v>
       </c>
       <c r="V73" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W73" s="3" t="n">
-        <v>68.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="X73" s="3" t="inlineStr">
         <is>
@@ -8576,64 +8568,64 @@
           <t>فريق 4</t>
         </is>
       </c>
-      <c r="E74" s="3" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 18:02</t>
-        </is>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H74" s="6" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-07 00:54</t>
-        </is>
-      </c>
-      <c r="J74" s="6" t="inlineStr">
+      <c r="E74" s="6" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-24 01:48</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="K74" s="3" t="n">
-        <v>82.2</v>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>2026-02-20 03:46</t>
-        </is>
-      </c>
-      <c r="M74" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="N74" s="3" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="O74" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-06 03:20</t>
-        </is>
-      </c>
-      <c r="P74" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="H74" s="3" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05 23:24</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K74" s="6" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="L74" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20 19:00</t>
+        </is>
+      </c>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
+        </is>
+      </c>
+      <c r="N74" s="6" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="O74" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-07 00:24</t>
+        </is>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="Q74" s="6" t="n">
-        <v>55.8</v>
+        <v>58.1</v>
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
-          <t>2026-03-21 01:30</t>
+          <t>2026-03-21 00:24</t>
         </is>
       </c>
       <c r="S74" s="6" t="inlineStr">
@@ -8645,17 +8637,17 @@
         <v>0</v>
       </c>
       <c r="U74" s="3" t="n">
-        <v>335</v>
+        <v>263.9</v>
       </c>
       <c r="V74" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W74" s="3" t="n">
-        <v>67</v>
-      </c>
-      <c r="X74" s="3" t="inlineStr">
-        <is>
-          <t>C</t>
+        <v>52.8</v>
+      </c>
+      <c r="X74" s="7" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y74" s="3" t="inlineStr">
@@ -8682,15 +8674,15 @@
       </c>
       <c r="D75" s="9" t="inlineStr">
         <is>
-          <t>فريق 4</t>
+          <t>فريق 5</t>
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>69.7</v>
+        <v>75.7</v>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>2026-01-23 18:02</t>
+          <t>2026-01-23 07:28</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -8698,25 +8690,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="H75" s="6" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-07 00:54</t>
-        </is>
-      </c>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="H75" s="3" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05 22:12</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="K75" s="3" t="n">
-        <v>82.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 03:46</t>
+          <t>2026-02-19 09:58</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
@@ -8725,11 +8717,11 @@
         </is>
       </c>
       <c r="N75" s="3" t="n">
-        <v>76.8</v>
+        <v>71.8</v>
       </c>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 03:20</t>
+          <t>2026-03-06 20:03</t>
         </is>
       </c>
       <c r="P75" s="3" t="inlineStr">
@@ -8737,34 +8729,34 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q75" s="6" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="R75" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-21 01:30</t>
-        </is>
-      </c>
-      <c r="S75" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q75" s="3" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="R75" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-20 12:12</t>
+        </is>
+      </c>
+      <c r="S75" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U75" s="3" t="n">
-        <v>335</v>
+        <v>380.6</v>
       </c>
       <c r="V75" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W75" s="3" t="n">
-        <v>67</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="X75" s="3" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y75" s="3" t="inlineStr">
@@ -8791,41 +8783,41 @@
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>فريق 4</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 18:02</t>
-        </is>
-      </c>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H76" s="6" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-07 00:54</t>
-        </is>
-      </c>
-      <c r="J76" s="6" t="inlineStr">
+          <t>فريق 3</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-24 01:48</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
+      <c r="H76" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:19</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
       <c r="K76" s="3" t="n">
-        <v>82.2</v>
+        <v>67.8</v>
       </c>
       <c r="L76" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 03:46</t>
+          <t>2026-02-19 14:31</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
@@ -8834,11 +8826,11 @@
         </is>
       </c>
       <c r="N76" s="3" t="n">
-        <v>76.8</v>
+        <v>76.2</v>
       </c>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 03:20</t>
+          <t>2026-03-05 08:19</t>
         </is>
       </c>
       <c r="P76" s="3" t="inlineStr">
@@ -8846,30 +8838,30 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q76" s="6" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="R76" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-21 01:30</t>
-        </is>
-      </c>
-      <c r="S76" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q76" s="3" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="R76" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19 08:02</t>
+        </is>
+      </c>
+      <c r="S76" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T76" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U76" s="3" t="n">
-        <v>335</v>
+        <v>339.2</v>
       </c>
       <c r="V76" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W76" s="3" t="n">
-        <v>67</v>
+        <v>67.8</v>
       </c>
       <c r="X76" s="3" t="inlineStr">
         <is>
@@ -8900,41 +8892,41 @@
       </c>
       <c r="D77" s="9" t="inlineStr">
         <is>
-          <t>فريق 4</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>69.7</v>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-23 18:02</t>
-        </is>
-      </c>
-      <c r="G77" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="H77" s="6" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-07 00:54</t>
-        </is>
-      </c>
-      <c r="J77" s="6" t="inlineStr">
+          <t>فريق 3</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-24 01:48</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
+      <c r="H77" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t>2026-02-05 13:19</t>
+        </is>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
       <c r="K77" s="3" t="n">
-        <v>82.2</v>
+        <v>67.8</v>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>2026-02-20 03:46</t>
+          <t>2026-02-19 14:31</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
@@ -8943,11 +8935,11 @@
         </is>
       </c>
       <c r="N77" s="3" t="n">
-        <v>76.8</v>
+        <v>76.2</v>
       </c>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>2026-03-06 03:20</t>
+          <t>2026-03-05 08:19</t>
         </is>
       </c>
       <c r="P77" s="3" t="inlineStr">
@@ -8955,30 +8947,30 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="Q77" s="6" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="R77" s="6" t="inlineStr">
-        <is>
-          <t>2026-03-21 01:30</t>
-        </is>
-      </c>
-      <c r="S77" s="6" t="inlineStr">
-        <is>
-          <t>نعم</t>
+      <c r="Q77" s="3" t="n">
+        <v>78.7</v>
+      </c>
+      <c r="R77" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-19 08:02</t>
+        </is>
+      </c>
+      <c r="S77" s="3" t="inlineStr">
+        <is>
+          <t>لا</t>
         </is>
       </c>
       <c r="T77" s="3" t="n">
         <v>0</v>
       </c>
       <c r="U77" s="3" t="n">
-        <v>335</v>
+        <v>339.2</v>
       </c>
       <c r="V77" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W77" s="3" t="n">
-        <v>67</v>
+        <v>67.8</v>
       </c>
       <c r="X77" s="3" t="inlineStr">
         <is>
@@ -9009,15 +9001,15 @@
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>فريق 5</t>
+          <t>فريق 2</t>
         </is>
       </c>
       <c r="E78" s="3" t="n">
-        <v>64.2</v>
+        <v>78.3</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 19:20</t>
+          <t>2026-01-22 13:31</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -9026,11 +9018,11 @@
         </is>
       </c>
       <c r="H78" s="3" t="n">
-        <v>72</v>
+        <v>81.3</v>
       </c>
       <c r="I78" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 04:38</t>
+          <t>2026-02-05 19:07</t>
         </is>
       </c>
       <c r="J78" s="3" t="inlineStr">
@@ -9039,11 +9031,11 @@
         </is>
       </c>
       <c r="K78" s="3" t="n">
-        <v>82.3</v>
+        <v>75.8</v>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 12:26</t>
+          <t>2026-02-19 07:08</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
@@ -9051,25 +9043,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N78" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="O78" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 03:45</t>
-        </is>
-      </c>
-      <c r="P78" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N78" s="6" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="O78" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-06 19:12</t>
+        </is>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="Q78" s="3" t="n">
-        <v>86.5</v>
+        <v>78.2</v>
       </c>
       <c r="R78" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 10:21</t>
+          <t>2026-03-20 15:10</t>
         </is>
       </c>
       <c r="S78" s="3" t="inlineStr">
@@ -9081,17 +9073,17 @@
         <v>0</v>
       </c>
       <c r="U78" s="3" t="n">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="V78" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W78" s="3" t="n">
-        <v>76.2</v>
+        <v>74.2</v>
       </c>
       <c r="X78" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y78" s="3" t="inlineStr">
@@ -9118,15 +9110,15 @@
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>فريق 5</t>
+          <t>فريق 2</t>
         </is>
       </c>
       <c r="E79" s="3" t="n">
-        <v>64.2</v>
+        <v>78.3</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 19:20</t>
+          <t>2026-01-22 13:31</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -9135,11 +9127,11 @@
         </is>
       </c>
       <c r="H79" s="3" t="n">
-        <v>72</v>
+        <v>81.3</v>
       </c>
       <c r="I79" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 04:38</t>
+          <t>2026-02-05 19:07</t>
         </is>
       </c>
       <c r="J79" s="3" t="inlineStr">
@@ -9148,11 +9140,11 @@
         </is>
       </c>
       <c r="K79" s="3" t="n">
-        <v>82.3</v>
+        <v>75.8</v>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 12:26</t>
+          <t>2026-02-19 07:08</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
@@ -9160,25 +9152,25 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="N79" s="3" t="n">
-        <v>76</v>
-      </c>
-      <c r="O79" s="3" t="inlineStr">
-        <is>
-          <t>2026-03-05 03:45</t>
-        </is>
-      </c>
-      <c r="P79" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+      <c r="N79" s="6" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="O79" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-06 19:12</t>
+        </is>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="Q79" s="3" t="n">
-        <v>86.5</v>
+        <v>78.2</v>
       </c>
       <c r="R79" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 10:21</t>
+          <t>2026-03-20 15:10</t>
         </is>
       </c>
       <c r="S79" s="3" t="inlineStr">
@@ -9190,17 +9182,17 @@
         <v>0</v>
       </c>
       <c r="U79" s="3" t="n">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="V79" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W79" s="3" t="n">
-        <v>76.2</v>
+        <v>74.2</v>
       </c>
       <c r="X79" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y79" s="3" t="inlineStr">
@@ -9227,15 +9219,15 @@
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>فريق 5</t>
+          <t>فريق 6</t>
         </is>
       </c>
       <c r="E80" s="3" t="n">
-        <v>64.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22 19:20</t>
+          <t>2026-01-22 13:26</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -9244,11 +9236,11 @@
         </is>
       </c>
       <c r="H80" s="3" t="n">
-        <v>72</v>
+        <v>66.7</v>
       </c>
       <c r="I80" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 04:38</t>
+          <t>2026-02-06 05:40</t>
         </is>
       </c>
       <c r="J80" s="3" t="inlineStr">
@@ -9257,11 +9249,11 @@
         </is>
       </c>
       <c r="K80" s="3" t="n">
-        <v>82.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="L80" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 12:26</t>
+          <t>2026-02-20 04:46</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
@@ -9270,11 +9262,11 @@
         </is>
       </c>
       <c r="N80" s="3" t="n">
-        <v>76</v>
+        <v>68.5</v>
       </c>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 03:45</t>
+          <t>2026-03-05 07:48</t>
         </is>
       </c>
       <c r="P80" s="3" t="inlineStr">
@@ -9283,11 +9275,11 @@
         </is>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>86.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="R80" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 10:21</t>
+          <t>2026-03-19 17:51</t>
         </is>
       </c>
       <c r="S80" s="3" t="inlineStr">
@@ -9299,17 +9291,17 @@
         <v>0</v>
       </c>
       <c r="U80" s="3" t="n">
-        <v>381</v>
+        <v>357</v>
       </c>
       <c r="V80" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W80" s="3" t="n">
-        <v>76.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="X80" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="Y80" s="3" t="inlineStr">
@@ -9336,28 +9328,28 @@
       </c>
       <c r="D81" s="9" t="inlineStr">
         <is>
-          <t>فريق 5</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>64.2</v>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>2026-01-22 19:20</t>
-        </is>
-      </c>
-      <c r="G81" s="3" t="inlineStr">
-        <is>
-          <t>لا</t>
+          <t>فريق 3</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-24 01:48</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>نعم</t>
         </is>
       </c>
       <c r="H81" s="3" t="n">
-        <v>72</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I81" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05 04:38</t>
+          <t>2026-02-05 13:19</t>
         </is>
       </c>
       <c r="J81" s="3" t="inlineStr">
@@ -9366,11 +9358,11 @@
         </is>
       </c>
       <c r="K81" s="3" t="n">
-        <v>82.3</v>
+        <v>67.8</v>
       </c>
       <c r="L81" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19 12:26</t>
+          <t>2026-02-19 14:31</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
@@ -9379,11 +9371,11 @@
         </is>
       </c>
       <c r="N81" s="3" t="n">
-        <v>76</v>
+        <v>76.2</v>
       </c>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>2026-03-05 03:45</t>
+          <t>2026-03-05 08:19</t>
         </is>
       </c>
       <c r="P81" s="3" t="inlineStr">
@@ -9392,11 +9384,11 @@
         </is>
       </c>
       <c r="Q81" s="3" t="n">
-        <v>86.5</v>
+        <v>78.7</v>
       </c>
       <c r="R81" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19 10:21</t>
+          <t>2026-03-19 08:02</t>
         </is>
       </c>
       <c r="S81" s="3" t="inlineStr">
@@ -9408,17 +9400,17 @@
         <v>0</v>
       </c>
       <c r="U81" s="3" t="n">
-        <v>381</v>
+        <v>339.2</v>
       </c>
       <c r="V81" s="3" t="n">
         <v>500</v>
       </c>
       <c r="W81" s="3" t="n">
-        <v>76.2</v>
+        <v>67.8</v>
       </c>
       <c r="X81" s="3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y81" s="3" t="inlineStr">
@@ -9449,11 +9441,11 @@
         </is>
       </c>
       <c r="E82" s="11" t="n">
-        <v>58.9</v>
+        <v>40.3</v>
       </c>
       <c r="F82" s="11" t="inlineStr">
         <is>
-          <t>2026-01-22 10:30</t>
+          <t>2026-01-21 10:34</t>
         </is>
       </c>
       <c r="G82" s="11" t="inlineStr">
@@ -9462,11 +9454,11 @@
         </is>
       </c>
       <c r="H82" s="11" t="n">
-        <v>45.1</v>
+        <v>35.4</v>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>2026-02-06 09:19</t>
+          <t>2026-02-06 18:50</t>
         </is>
       </c>
       <c r="J82" s="11" t="inlineStr">
@@ -9474,28 +9466,58 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K82" s="12" t="inlineStr"/>
-      <c r="L82" s="12" t="inlineStr"/>
-      <c r="M82" s="12" t="inlineStr"/>
-      <c r="N82" s="12" t="inlineStr"/>
-      <c r="O82" s="12" t="inlineStr"/>
-      <c r="P82" s="12" t="inlineStr"/>
-      <c r="Q82" s="12" t="inlineStr"/>
-      <c r="R82" s="12" t="inlineStr"/>
-      <c r="S82" s="12" t="inlineStr"/>
+      <c r="K82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M82" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P82" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q82" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S82" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T82" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U82" s="11" t="n">
-        <v>104</v>
+        <v>75.7</v>
       </c>
       <c r="V82" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W82" s="11" t="n">
-        <v>52</v>
-      </c>
-      <c r="X82" s="13" t="inlineStr">
+        <v>15.1</v>
+      </c>
+      <c r="X82" s="12" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -9528,11 +9550,11 @@
         </is>
       </c>
       <c r="E83" s="11" t="n">
-        <v>64.90000000000001</v>
+        <v>60.2</v>
       </c>
       <c r="F83" s="11" t="inlineStr">
         <is>
-          <t>2026-01-23 16:15</t>
+          <t>2026-01-20 15:09</t>
         </is>
       </c>
       <c r="G83" s="11" t="inlineStr">
@@ -9541,11 +9563,11 @@
         </is>
       </c>
       <c r="H83" s="11" t="n">
-        <v>56.7</v>
+        <v>67</v>
       </c>
       <c r="I83" s="11" t="inlineStr">
         <is>
-          <t>2026-02-04 17:14</t>
+          <t>2026-02-05 22:51</t>
         </is>
       </c>
       <c r="J83" s="11" t="inlineStr">
@@ -9553,30 +9575,60 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K83" s="12" t="inlineStr"/>
-      <c r="L83" s="12" t="inlineStr"/>
-      <c r="M83" s="12" t="inlineStr"/>
-      <c r="N83" s="12" t="inlineStr"/>
-      <c r="O83" s="12" t="inlineStr"/>
-      <c r="P83" s="12" t="inlineStr"/>
-      <c r="Q83" s="12" t="inlineStr"/>
-      <c r="R83" s="12" t="inlineStr"/>
-      <c r="S83" s="12" t="inlineStr"/>
+      <c r="K83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M83" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P83" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q83" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R83" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S83" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T83" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U83" s="11" t="n">
-        <v>121.6</v>
+        <v>127.2</v>
       </c>
       <c r="V83" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W83" s="11" t="n">
-        <v>60.8</v>
-      </c>
-      <c r="X83" s="11" t="inlineStr">
-        <is>
-          <t>D+</t>
+        <v>25.4</v>
+      </c>
+      <c r="X83" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y83" s="11" t="inlineStr">
@@ -9607,11 +9659,11 @@
         </is>
       </c>
       <c r="E84" s="11" t="n">
-        <v>47.1</v>
+        <v>59.1</v>
       </c>
       <c r="F84" s="11" t="inlineStr">
         <is>
-          <t>2026-01-21 19:19</t>
+          <t>2026-01-23 22:36</t>
         </is>
       </c>
       <c r="G84" s="11" t="inlineStr">
@@ -9620,11 +9672,11 @@
         </is>
       </c>
       <c r="H84" s="11" t="n">
-        <v>51.8</v>
+        <v>56.8</v>
       </c>
       <c r="I84" s="11" t="inlineStr">
         <is>
-          <t>2026-02-04 15:02</t>
+          <t>2026-02-03 10:21</t>
         </is>
       </c>
       <c r="J84" s="11" t="inlineStr">
@@ -9632,28 +9684,58 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K84" s="12" t="inlineStr"/>
-      <c r="L84" s="12" t="inlineStr"/>
-      <c r="M84" s="12" t="inlineStr"/>
-      <c r="N84" s="12" t="inlineStr"/>
-      <c r="O84" s="12" t="inlineStr"/>
-      <c r="P84" s="12" t="inlineStr"/>
-      <c r="Q84" s="12" t="inlineStr"/>
-      <c r="R84" s="12" t="inlineStr"/>
-      <c r="S84" s="12" t="inlineStr"/>
+      <c r="K84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M84" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P84" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q84" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R84" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S84" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T84" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U84" s="11" t="n">
-        <v>98.90000000000001</v>
+        <v>115.9</v>
       </c>
       <c r="V84" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W84" s="11" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="X84" s="13" t="inlineStr">
+        <v>23.2</v>
+      </c>
+      <c r="X84" s="12" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -9686,11 +9768,11 @@
         </is>
       </c>
       <c r="E85" s="11" t="n">
-        <v>50.5</v>
+        <v>52.1</v>
       </c>
       <c r="F85" s="11" t="inlineStr">
         <is>
-          <t>2026-01-22 17:02</t>
+          <t>2026-01-21 10:36</t>
         </is>
       </c>
       <c r="G85" s="11" t="inlineStr">
@@ -9699,11 +9781,11 @@
         </is>
       </c>
       <c r="H85" s="11" t="n">
-        <v>63.2</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I85" s="11" t="inlineStr">
         <is>
-          <t>2026-02-05 09:55</t>
+          <t>2026-02-04 16:24</t>
         </is>
       </c>
       <c r="J85" s="11" t="inlineStr">
@@ -9711,30 +9793,60 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K85" s="12" t="inlineStr"/>
-      <c r="L85" s="12" t="inlineStr"/>
-      <c r="M85" s="12" t="inlineStr"/>
-      <c r="N85" s="12" t="inlineStr"/>
-      <c r="O85" s="12" t="inlineStr"/>
-      <c r="P85" s="12" t="inlineStr"/>
-      <c r="Q85" s="12" t="inlineStr"/>
-      <c r="R85" s="12" t="inlineStr"/>
-      <c r="S85" s="12" t="inlineStr"/>
+      <c r="K85" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M85" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P85" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q85" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S85" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T85" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U85" s="11" t="n">
-        <v>113.7</v>
+        <v>118.5</v>
       </c>
       <c r="V85" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W85" s="11" t="n">
-        <v>56.9</v>
-      </c>
-      <c r="X85" s="11" t="inlineStr">
-        <is>
-          <t>D</t>
+        <v>23.7</v>
+      </c>
+      <c r="X85" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y85" s="11" t="inlineStr">
@@ -9744,45 +9856,45 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="14" t="inlineStr">
+      <c r="A86" s="13" t="inlineStr">
         <is>
           <t>STD-085</t>
         </is>
       </c>
-      <c r="B86" s="14" t="inlineStr">
+      <c r="B86" s="13" t="inlineStr">
         <is>
           <t>نيرة سامي</t>
         </is>
       </c>
-      <c r="C86" s="14" t="inlineStr">
+      <c r="C86" s="13" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="D86" s="14" t="inlineStr">
+      <c r="D86" s="13" t="inlineStr">
         <is>
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E86" s="15" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="F86" s="15" t="inlineStr">
-        <is>
-          <t>2026-01-23 23:42</t>
-        </is>
-      </c>
-      <c r="G86" s="15" t="inlineStr">
+      <c r="E86" s="14" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="F86" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-23 23:12</t>
+        </is>
+      </c>
+      <c r="G86" s="14" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
       <c r="H86" s="11" t="n">
-        <v>69</v>
+        <v>65.3</v>
       </c>
       <c r="I86" s="11" t="inlineStr">
         <is>
-          <t>2026-02-06 23:00</t>
+          <t>2026-02-06 08:45</t>
         </is>
       </c>
       <c r="J86" s="11" t="inlineStr">
@@ -9790,28 +9902,58 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K86" s="12" t="inlineStr"/>
-      <c r="L86" s="12" t="inlineStr"/>
-      <c r="M86" s="12" t="inlineStr"/>
-      <c r="N86" s="12" t="inlineStr"/>
-      <c r="O86" s="12" t="inlineStr"/>
-      <c r="P86" s="12" t="inlineStr"/>
-      <c r="Q86" s="12" t="inlineStr"/>
-      <c r="R86" s="12" t="inlineStr"/>
-      <c r="S86" s="12" t="inlineStr"/>
+      <c r="K86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M86" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O86" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P86" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q86" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S86" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T86" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U86" s="11" t="n">
-        <v>94.5</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="V86" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W86" s="11" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="X86" s="13" t="inlineStr">
+        <v>18.5</v>
+      </c>
+      <c r="X86" s="12" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -9823,74 +9965,104 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="14" t="inlineStr">
+      <c r="A87" s="13" t="inlineStr">
         <is>
           <t>STD-086</t>
         </is>
       </c>
-      <c r="B87" s="14" t="inlineStr">
+      <c r="B87" s="13" t="inlineStr">
         <is>
           <t>إيمان زكي</t>
         </is>
       </c>
-      <c r="C87" s="14" t="inlineStr">
+      <c r="C87" s="13" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="D87" s="14" t="inlineStr">
+      <c r="D87" s="13" t="inlineStr">
         <is>
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E87" s="15" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="F87" s="15" t="inlineStr">
-        <is>
-          <t>2026-01-24 01:12</t>
-        </is>
-      </c>
-      <c r="G87" s="15" t="inlineStr">
+      <c r="E87" s="11" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F87" s="11" t="inlineStr">
+        <is>
+          <t>2026-01-22 20:00</t>
+        </is>
+      </c>
+      <c r="G87" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H87" s="14" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="I87" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-07 10:06</t>
+        </is>
+      </c>
+      <c r="J87" s="14" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H87" s="11" t="n">
-        <v>45.2</v>
-      </c>
-      <c r="I87" s="11" t="inlineStr">
-        <is>
-          <t>2026-02-06 08:36</t>
-        </is>
-      </c>
-      <c r="J87" s="11" t="inlineStr">
-        <is>
-          <t>لا</t>
-        </is>
-      </c>
-      <c r="K87" s="12" t="inlineStr"/>
-      <c r="L87" s="12" t="inlineStr"/>
-      <c r="M87" s="12" t="inlineStr"/>
-      <c r="N87" s="12" t="inlineStr"/>
-      <c r="O87" s="12" t="inlineStr"/>
-      <c r="P87" s="12" t="inlineStr"/>
-      <c r="Q87" s="12" t="inlineStr"/>
-      <c r="R87" s="12" t="inlineStr"/>
-      <c r="S87" s="12" t="inlineStr"/>
+      <c r="K87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M87" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P87" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q87" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R87" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S87" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T87" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U87" s="11" t="n">
-        <v>69.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="V87" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W87" s="11" t="n">
-        <v>34.9</v>
-      </c>
-      <c r="X87" s="13" t="inlineStr">
+        <v>15.1</v>
+      </c>
+      <c r="X87" s="12" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -9902,74 +10074,104 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="14" t="inlineStr">
+      <c r="A88" s="13" t="inlineStr">
         <is>
           <t>STD-087</t>
         </is>
       </c>
-      <c r="B88" s="14" t="inlineStr">
+      <c r="B88" s="13" t="inlineStr">
         <is>
           <t>أسماء حافظ</t>
         </is>
       </c>
-      <c r="C88" s="14" t="inlineStr">
+      <c r="C88" s="13" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="D88" s="14" t="inlineStr">
+      <c r="D88" s="13" t="inlineStr">
         <is>
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E88" s="15" t="n">
-        <v>31.2</v>
-      </c>
-      <c r="F88" s="15" t="inlineStr">
-        <is>
-          <t>2026-01-24 10:18</t>
-        </is>
-      </c>
-      <c r="G88" s="15" t="inlineStr">
+      <c r="E88" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="F88" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-24 01:42</t>
+        </is>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H88" s="15" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="I88" s="15" t="inlineStr">
-        <is>
-          <t>2026-02-06 19:42</t>
-        </is>
-      </c>
-      <c r="J88" s="15" t="inlineStr">
+      <c r="H88" s="14" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="I88" s="14" t="inlineStr">
+        <is>
+          <t>2026-02-06 21:42</t>
+        </is>
+      </c>
+      <c r="J88" s="14" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="K88" s="12" t="inlineStr"/>
-      <c r="L88" s="12" t="inlineStr"/>
-      <c r="M88" s="12" t="inlineStr"/>
-      <c r="N88" s="12" t="inlineStr"/>
-      <c r="O88" s="12" t="inlineStr"/>
-      <c r="P88" s="12" t="inlineStr"/>
-      <c r="Q88" s="12" t="inlineStr"/>
-      <c r="R88" s="12" t="inlineStr"/>
-      <c r="S88" s="12" t="inlineStr"/>
+      <c r="K88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M88" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P88" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q88" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S88" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T88" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U88" s="11" t="n">
-        <v>83.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="V88" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W88" s="11" t="n">
-        <v>41.8</v>
-      </c>
-      <c r="X88" s="13" t="inlineStr">
+        <v>15.7</v>
+      </c>
+      <c r="X88" s="12" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -9981,76 +10183,106 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="14" t="inlineStr">
+      <c r="A89" s="13" t="inlineStr">
         <is>
           <t>STD-088</t>
         </is>
       </c>
-      <c r="B89" s="14" t="inlineStr">
+      <c r="B89" s="13" t="inlineStr">
         <is>
           <t>دعاء رمضان</t>
         </is>
       </c>
-      <c r="C89" s="14" t="inlineStr">
+      <c r="C89" s="13" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="D89" s="14" t="inlineStr">
+      <c r="D89" s="13" t="inlineStr">
         <is>
           <t>عمل فردي</t>
         </is>
       </c>
-      <c r="E89" s="15" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="F89" s="15" t="inlineStr">
-        <is>
-          <t>2026-01-23 21:00</t>
-        </is>
-      </c>
-      <c r="G89" s="15" t="inlineStr">
+      <c r="E89" s="14" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="F89" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-23 22:24</t>
+        </is>
+      </c>
+      <c r="G89" s="14" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H89" s="15" t="n">
-        <v>57.2</v>
-      </c>
-      <c r="I89" s="15" t="inlineStr">
-        <is>
-          <t>2026-02-07 00:24</t>
-        </is>
-      </c>
-      <c r="J89" s="15" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="K89" s="12" t="inlineStr"/>
-      <c r="L89" s="12" t="inlineStr"/>
-      <c r="M89" s="12" t="inlineStr"/>
-      <c r="N89" s="12" t="inlineStr"/>
-      <c r="O89" s="12" t="inlineStr"/>
-      <c r="P89" s="12" t="inlineStr"/>
-      <c r="Q89" s="12" t="inlineStr"/>
-      <c r="R89" s="12" t="inlineStr"/>
-      <c r="S89" s="12" t="inlineStr"/>
+      <c r="H89" s="11" t="n">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="I89" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-06 10:06</t>
+        </is>
+      </c>
+      <c r="J89" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M89" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P89" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q89" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R89" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S89" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T89" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U89" s="11" t="n">
-        <v>110.8</v>
+        <v>137</v>
       </c>
       <c r="V89" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W89" s="11" t="n">
-        <v>55.4</v>
-      </c>
-      <c r="X89" s="11" t="inlineStr">
-        <is>
-          <t>D</t>
+        <v>27.4</v>
+      </c>
+      <c r="X89" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y89" s="11" t="inlineStr">
@@ -10060,32 +10292,32 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="16" t="inlineStr">
+      <c r="A90" s="15" t="inlineStr">
         <is>
           <t>STD-089</t>
         </is>
       </c>
-      <c r="B90" s="16" t="inlineStr">
+      <c r="B90" s="15" t="inlineStr">
         <is>
           <t>سلوى ممدوح</t>
         </is>
       </c>
-      <c r="C90" s="16" t="inlineStr">
+      <c r="C90" s="15" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="D90" s="16" t="inlineStr">
+      <c r="D90" s="15" t="inlineStr">
         <is>
           <t>فريق 6</t>
         </is>
       </c>
       <c r="E90" s="11" t="n">
-        <v>77.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="F90" s="11" t="inlineStr">
         <is>
-          <t>2026-01-21 10:36</t>
+          <t>2026-01-21 16:38</t>
         </is>
       </c>
       <c r="G90" s="11" t="inlineStr">
@@ -10094,11 +10326,11 @@
         </is>
       </c>
       <c r="H90" s="11" t="n">
-        <v>77.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>2026-02-04 16:24</t>
+          <t>2026-02-05 20:37</t>
         </is>
       </c>
       <c r="J90" s="11" t="inlineStr">
@@ -10106,30 +10338,60 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K90" s="12" t="inlineStr"/>
-      <c r="L90" s="12" t="inlineStr"/>
-      <c r="M90" s="12" t="inlineStr"/>
-      <c r="N90" s="12" t="inlineStr"/>
-      <c r="O90" s="12" t="inlineStr"/>
-      <c r="P90" s="12" t="inlineStr"/>
-      <c r="Q90" s="12" t="inlineStr"/>
-      <c r="R90" s="12" t="inlineStr"/>
-      <c r="S90" s="12" t="inlineStr"/>
+      <c r="K90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M90" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O90" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P90" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q90" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R90" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S90" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T90" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U90" s="11" t="n">
-        <v>155</v>
+        <v>149.2</v>
       </c>
       <c r="V90" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W90" s="11" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="X90" s="11" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>29.8</v>
+      </c>
+      <c r="X90" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y90" s="11" t="inlineStr">
@@ -10139,32 +10401,32 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="16" t="inlineStr">
+      <c r="A91" s="15" t="inlineStr">
         <is>
           <t>STD-090</t>
         </is>
       </c>
-      <c r="B91" s="16" t="inlineStr">
+      <c r="B91" s="15" t="inlineStr">
         <is>
           <t>هند ماهر</t>
         </is>
       </c>
-      <c r="C91" s="16" t="inlineStr">
+      <c r="C91" s="15" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="D91" s="16" t="inlineStr">
-        <is>
-          <t>فريق 6</t>
+      <c r="D91" s="15" t="inlineStr">
+        <is>
+          <t>فريق 4</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
-        <v>77.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="F91" s="11" t="inlineStr">
         <is>
-          <t>2026-01-21 10:36</t>
+          <t>2026-01-21 18:05</t>
         </is>
       </c>
       <c r="G91" s="11" t="inlineStr">
@@ -10173,11 +10435,11 @@
         </is>
       </c>
       <c r="H91" s="11" t="n">
-        <v>77.09999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>2026-02-04 16:24</t>
+          <t>2026-02-04 16:48</t>
         </is>
       </c>
       <c r="J91" s="11" t="inlineStr">
@@ -10185,30 +10447,60 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K91" s="12" t="inlineStr"/>
-      <c r="L91" s="12" t="inlineStr"/>
-      <c r="M91" s="12" t="inlineStr"/>
-      <c r="N91" s="12" t="inlineStr"/>
-      <c r="O91" s="12" t="inlineStr"/>
-      <c r="P91" s="12" t="inlineStr"/>
-      <c r="Q91" s="12" t="inlineStr"/>
-      <c r="R91" s="12" t="inlineStr"/>
-      <c r="S91" s="12" t="inlineStr"/>
+      <c r="K91" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M91" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P91" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q91" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S91" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T91" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U91" s="11" t="n">
-        <v>155</v>
+        <v>155.3</v>
       </c>
       <c r="V91" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W91" s="11" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="X91" s="11" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>31.1</v>
+      </c>
+      <c r="X91" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y91" s="11" t="inlineStr">
@@ -10218,32 +10510,32 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="16" t="inlineStr">
+      <c r="A92" s="15" t="inlineStr">
         <is>
           <t>STD-091</t>
         </is>
       </c>
-      <c r="B92" s="16" t="inlineStr">
+      <c r="B92" s="15" t="inlineStr">
         <is>
           <t>رانيا فريد</t>
         </is>
       </c>
-      <c r="C92" s="16" t="inlineStr">
+      <c r="C92" s="15" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="D92" s="16" t="inlineStr">
-        <is>
-          <t>فريق 6</t>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>فريق 5</t>
         </is>
       </c>
       <c r="E92" s="11" t="n">
-        <v>77.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="F92" s="11" t="inlineStr">
         <is>
-          <t>2026-01-21 10:36</t>
+          <t>2026-01-20 14:02</t>
         </is>
       </c>
       <c r="G92" s="11" t="inlineStr">
@@ -10252,11 +10544,11 @@
         </is>
       </c>
       <c r="H92" s="11" t="n">
-        <v>77.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>2026-02-04 16:24</t>
+          <t>2026-02-04 10:37</t>
         </is>
       </c>
       <c r="J92" s="11" t="inlineStr">
@@ -10264,30 +10556,60 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K92" s="12" t="inlineStr"/>
-      <c r="L92" s="12" t="inlineStr"/>
-      <c r="M92" s="12" t="inlineStr"/>
-      <c r="N92" s="12" t="inlineStr"/>
-      <c r="O92" s="12" t="inlineStr"/>
-      <c r="P92" s="12" t="inlineStr"/>
-      <c r="Q92" s="12" t="inlineStr"/>
-      <c r="R92" s="12" t="inlineStr"/>
-      <c r="S92" s="12" t="inlineStr"/>
+      <c r="K92" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M92" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P92" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q92" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S92" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T92" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U92" s="11" t="n">
-        <v>155</v>
+        <v>147.1</v>
       </c>
       <c r="V92" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W92" s="11" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="X92" s="11" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>29.4</v>
+      </c>
+      <c r="X92" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y92" s="11" t="inlineStr">
@@ -10297,32 +10619,32 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="16" t="inlineStr">
+      <c r="A93" s="15" t="inlineStr">
         <is>
           <t>STD-092</t>
         </is>
       </c>
-      <c r="B93" s="16" t="inlineStr">
+      <c r="B93" s="15" t="inlineStr">
         <is>
           <t>عزة طلعت</t>
         </is>
       </c>
-      <c r="C93" s="16" t="inlineStr">
+      <c r="C93" s="15" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="D93" s="16" t="inlineStr">
-        <is>
-          <t>فريق 6</t>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>فريق 1</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
-        <v>77.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F93" s="11" t="inlineStr">
         <is>
-          <t>2026-01-21 10:36</t>
+          <t>2026-01-19 21:17</t>
         </is>
       </c>
       <c r="G93" s="11" t="inlineStr">
@@ -10331,11 +10653,11 @@
         </is>
       </c>
       <c r="H93" s="11" t="n">
-        <v>77.09999999999999</v>
+        <v>91</v>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>2026-02-04 16:24</t>
+          <t>2026-02-05 15:23</t>
         </is>
       </c>
       <c r="J93" s="11" t="inlineStr">
@@ -10343,30 +10665,60 @@
           <t>لا</t>
         </is>
       </c>
-      <c r="K93" s="12" t="inlineStr"/>
-      <c r="L93" s="12" t="inlineStr"/>
-      <c r="M93" s="12" t="inlineStr"/>
-      <c r="N93" s="12" t="inlineStr"/>
-      <c r="O93" s="12" t="inlineStr"/>
-      <c r="P93" s="12" t="inlineStr"/>
-      <c r="Q93" s="12" t="inlineStr"/>
-      <c r="R93" s="12" t="inlineStr"/>
-      <c r="S93" s="12" t="inlineStr"/>
+      <c r="K93" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M93" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P93" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q93" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S93" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T93" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U93" s="11" t="n">
-        <v>155</v>
+        <v>173.4</v>
       </c>
       <c r="V93" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W93" s="11" t="n">
-        <v>77.5</v>
-      </c>
-      <c r="X93" s="11" t="inlineStr">
-        <is>
-          <t>B</t>
+        <v>34.7</v>
+      </c>
+      <c r="X93" s="12" t="inlineStr">
+        <is>
+          <t>F</t>
         </is>
       </c>
       <c r="Y93" s="11" t="inlineStr">
@@ -10376,74 +10728,104 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="17" t="inlineStr">
+      <c r="A94" s="16" t="inlineStr">
         <is>
           <t>STD-093</t>
         </is>
       </c>
-      <c r="B94" s="17" t="inlineStr">
+      <c r="B94" s="16" t="inlineStr">
         <is>
           <t>منار شوقي</t>
         </is>
       </c>
-      <c r="C94" s="17" t="inlineStr">
+      <c r="C94" s="16" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="D94" s="17" t="inlineStr">
-        <is>
-          <t>فريق 6</t>
-        </is>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F94" s="15" t="inlineStr">
-        <is>
-          <t>2026-01-24 09:54</t>
-        </is>
-      </c>
-      <c r="G94" s="15" t="inlineStr">
+      <c r="D94" s="16" t="inlineStr">
+        <is>
+          <t>فريق 4</t>
+        </is>
+      </c>
+      <c r="E94" s="14" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="F94" s="14" t="inlineStr">
+        <is>
+          <t>2026-01-24 01:48</t>
+        </is>
+      </c>
+      <c r="G94" s="14" t="inlineStr">
         <is>
           <t>نعم</t>
         </is>
       </c>
-      <c r="H94" s="15" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="I94" s="15" t="inlineStr">
-        <is>
-          <t>2026-02-07 01:48</t>
-        </is>
-      </c>
-      <c r="J94" s="15" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="K94" s="12" t="inlineStr"/>
-      <c r="L94" s="12" t="inlineStr"/>
-      <c r="M94" s="12" t="inlineStr"/>
-      <c r="N94" s="12" t="inlineStr"/>
-      <c r="O94" s="12" t="inlineStr"/>
-      <c r="P94" s="12" t="inlineStr"/>
-      <c r="Q94" s="12" t="inlineStr"/>
-      <c r="R94" s="12" t="inlineStr"/>
-      <c r="S94" s="12" t="inlineStr"/>
+      <c r="H94" s="11" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="I94" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-05 23:24</t>
+        </is>
+      </c>
+      <c r="J94" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M94" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P94" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q94" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R94" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S94" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T94" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U94" s="11" t="n">
-        <v>58.5</v>
+        <v>122.5</v>
       </c>
       <c r="V94" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W94" s="11" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="X94" s="13" t="inlineStr">
+        <v>24.5</v>
+      </c>
+      <c r="X94" s="12" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -10455,74 +10837,104 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="17" t="inlineStr">
+      <c r="A95" s="16" t="inlineStr">
         <is>
           <t>STD-094</t>
         </is>
       </c>
-      <c r="B95" s="17" t="inlineStr">
+      <c r="B95" s="16" t="inlineStr">
         <is>
           <t>نادين عصام</t>
         </is>
       </c>
-      <c r="C95" s="17" t="inlineStr">
+      <c r="C95" s="16" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="D95" s="17" t="inlineStr">
-        <is>
-          <t>فريق 6</t>
-        </is>
-      </c>
-      <c r="E95" s="15" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F95" s="15" t="inlineStr">
-        <is>
-          <t>2026-01-24 09:54</t>
-        </is>
-      </c>
-      <c r="G95" s="15" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H95" s="15" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="I95" s="15" t="inlineStr">
-        <is>
-          <t>2026-02-07 01:48</t>
-        </is>
-      </c>
-      <c r="J95" s="15" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="K95" s="12" t="inlineStr"/>
-      <c r="L95" s="12" t="inlineStr"/>
-      <c r="M95" s="12" t="inlineStr"/>
-      <c r="N95" s="12" t="inlineStr"/>
-      <c r="O95" s="12" t="inlineStr"/>
-      <c r="P95" s="12" t="inlineStr"/>
-      <c r="Q95" s="12" t="inlineStr"/>
-      <c r="R95" s="12" t="inlineStr"/>
-      <c r="S95" s="12" t="inlineStr"/>
+      <c r="D95" s="16" t="inlineStr">
+        <is>
+          <t>فريق 2</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="F95" s="11" t="inlineStr">
+        <is>
+          <t>2026-01-22 13:31</t>
+        </is>
+      </c>
+      <c r="G95" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H95" s="11" t="n">
+        <v>81.3</v>
+      </c>
+      <c r="I95" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-05 19:07</t>
+        </is>
+      </c>
+      <c r="J95" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M95" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P95" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q95" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S95" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T95" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U95" s="11" t="n">
-        <v>58.5</v>
+        <v>159.6</v>
       </c>
       <c r="V95" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W95" s="11" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="X95" s="13" t="inlineStr">
+        <v>31.9</v>
+      </c>
+      <c r="X95" s="12" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -10534,74 +10946,104 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="17" t="inlineStr">
+      <c r="A96" s="16" t="inlineStr">
         <is>
           <t>STD-095</t>
         </is>
       </c>
-      <c r="B96" s="17" t="inlineStr">
+      <c r="B96" s="16" t="inlineStr">
         <is>
           <t>شهد كمال</t>
         </is>
       </c>
-      <c r="C96" s="17" t="inlineStr">
+      <c r="C96" s="16" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="D96" s="17" t="inlineStr">
-        <is>
-          <t>فريق 6</t>
-        </is>
-      </c>
-      <c r="E96" s="15" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F96" s="15" t="inlineStr">
-        <is>
-          <t>2026-01-24 09:54</t>
-        </is>
-      </c>
-      <c r="G96" s="15" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H96" s="15" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="I96" s="15" t="inlineStr">
-        <is>
-          <t>2026-02-07 01:48</t>
-        </is>
-      </c>
-      <c r="J96" s="15" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="K96" s="12" t="inlineStr"/>
-      <c r="L96" s="12" t="inlineStr"/>
-      <c r="M96" s="12" t="inlineStr"/>
-      <c r="N96" s="12" t="inlineStr"/>
-      <c r="O96" s="12" t="inlineStr"/>
-      <c r="P96" s="12" t="inlineStr"/>
-      <c r="Q96" s="12" t="inlineStr"/>
-      <c r="R96" s="12" t="inlineStr"/>
-      <c r="S96" s="12" t="inlineStr"/>
+      <c r="D96" s="16" t="inlineStr">
+        <is>
+          <t>فريق 5</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="F96" s="11" t="inlineStr">
+        <is>
+          <t>2026-01-23 07:28</t>
+        </is>
+      </c>
+      <c r="G96" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H96" s="11" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="I96" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-05 22:12</t>
+        </is>
+      </c>
+      <c r="J96" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M96" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P96" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R96" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S96" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T96" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U96" s="11" t="n">
-        <v>58.5</v>
+        <v>152.8</v>
       </c>
       <c r="V96" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W96" s="11" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="X96" s="13" t="inlineStr">
+        <v>30.6</v>
+      </c>
+      <c r="X96" s="12" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -10613,74 +11055,104 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="17" t="inlineStr">
+      <c r="A97" s="16" t="inlineStr">
         <is>
           <t>STD-096</t>
         </is>
       </c>
-      <c r="B97" s="17" t="inlineStr">
+      <c r="B97" s="16" t="inlineStr">
         <is>
           <t>فاطمة سعيد</t>
         </is>
       </c>
-      <c r="C97" s="17" t="inlineStr">
+      <c r="C97" s="16" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="D97" s="17" t="inlineStr">
-        <is>
-          <t>فريق 6</t>
-        </is>
-      </c>
-      <c r="E97" s="15" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="F97" s="15" t="inlineStr">
-        <is>
-          <t>2026-01-24 09:54</t>
-        </is>
-      </c>
-      <c r="G97" s="15" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="H97" s="15" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="I97" s="15" t="inlineStr">
-        <is>
-          <t>2026-02-07 01:48</t>
-        </is>
-      </c>
-      <c r="J97" s="15" t="inlineStr">
-        <is>
-          <t>نعم</t>
-        </is>
-      </c>
-      <c r="K97" s="12" t="inlineStr"/>
-      <c r="L97" s="12" t="inlineStr"/>
-      <c r="M97" s="12" t="inlineStr"/>
-      <c r="N97" s="12" t="inlineStr"/>
-      <c r="O97" s="12" t="inlineStr"/>
-      <c r="P97" s="12" t="inlineStr"/>
-      <c r="Q97" s="12" t="inlineStr"/>
-      <c r="R97" s="12" t="inlineStr"/>
-      <c r="S97" s="12" t="inlineStr"/>
+      <c r="D97" s="16" t="inlineStr">
+        <is>
+          <t>فريق 1</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v>74.8</v>
+      </c>
+      <c r="F97" s="11" t="inlineStr">
+        <is>
+          <t>2026-01-22 05:09</t>
+        </is>
+      </c>
+      <c r="G97" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="H97" s="11" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="I97" s="11" t="inlineStr">
+        <is>
+          <t>2026-02-06 01:24</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="inlineStr">
+        <is>
+          <t>لا</t>
+        </is>
+      </c>
+      <c r="K97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="M97" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="P97" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q97" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" s="11" t="inlineStr">
+        <is>
+          <t>لم يتم التسليم</t>
+        </is>
+      </c>
+      <c r="S97" s="11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="T97" s="11" t="n">
         <v>0</v>
       </c>
       <c r="U97" s="11" t="n">
-        <v>58.5</v>
+        <v>145</v>
       </c>
       <c r="V97" s="11" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="W97" s="11" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="X97" s="13" t="inlineStr">
+        <v>29</v>
+      </c>
+      <c r="X97" s="12" t="inlineStr">
         <is>
           <t>F</t>
         </is>
@@ -10720,233 +11192,233 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Group</t>
         </is>
       </c>
-      <c r="B1" s="18" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C1" s="18" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="D1" s="18" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>N_Active</t>
         </is>
       </c>
-      <c r="E1" s="18" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t>M1_Mean</t>
         </is>
       </c>
-      <c r="F1" s="18" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>M2_Mean</t>
         </is>
       </c>
-      <c r="G1" s="18" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>M3_Mean</t>
         </is>
       </c>
-      <c r="H1" s="18" t="inlineStr">
+      <c r="H1" s="17" t="inlineStr">
         <is>
           <t>M4_Mean</t>
         </is>
       </c>
-      <c r="I1" s="18" t="inlineStr">
+      <c r="I1" s="17" t="inlineStr">
         <is>
           <t>M5_Mean</t>
         </is>
       </c>
-      <c r="J1" s="18" t="inlineStr">
+      <c r="J1" s="17" t="inlineStr">
         <is>
           <t>Total_Mean</t>
         </is>
       </c>
-      <c r="K1" s="18" t="inlineStr">
+      <c r="K1" s="17" t="inlineStr">
         <is>
           <t>Pct_Mean</t>
         </is>
       </c>
-      <c r="L1" s="18" t="inlineStr">
+      <c r="L1" s="17" t="inlineStr">
         <is>
           <t>Late_Count</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>G1</t>
         </is>
       </c>
-      <c r="B2" s="19" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>تنافسي+مفتوح</t>
         </is>
       </c>
-      <c r="C2" s="19" t="n">
+      <c r="C2" s="18" t="n">
         <v>24</v>
       </c>
-      <c r="D2" s="19" t="n">
+      <c r="D2" s="18" t="n">
         <v>20</v>
       </c>
-      <c r="E2" s="19" t="n">
-        <v>69.19</v>
-      </c>
-      <c r="F2" s="19" t="n">
-        <v>69.56999999999999</v>
-      </c>
-      <c r="G2" s="19" t="n">
-        <v>74.8</v>
-      </c>
-      <c r="H2" s="19" t="n">
-        <v>79.04000000000001</v>
-      </c>
-      <c r="I2" s="19" t="n">
-        <v>77.54000000000001</v>
-      </c>
-      <c r="J2" s="19" t="n">
-        <v>334.49</v>
-      </c>
-      <c r="K2" s="19" t="n">
-        <v>72.38</v>
-      </c>
-      <c r="L2" s="19" t="n">
+      <c r="E2" s="18" t="n">
+        <v>68.79000000000001</v>
+      </c>
+      <c r="F2" s="18" t="n">
+        <v>69.93000000000001</v>
+      </c>
+      <c r="G2" s="18" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="H2" s="18" t="n">
+        <v>65.86</v>
+      </c>
+      <c r="I2" s="18" t="n">
+        <v>64.62</v>
+      </c>
+      <c r="J2" s="18" t="n">
+        <v>334.45</v>
+      </c>
+      <c r="K2" s="18" t="n">
+        <v>66.89</v>
+      </c>
+      <c r="L2" s="18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="inlineStr">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>G2</t>
         </is>
       </c>
-      <c r="B3" s="20" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>تنافسي+محدد</t>
         </is>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="C3" s="19" t="n">
         <v>24</v>
       </c>
-      <c r="D3" s="20" t="n">
+      <c r="D3" s="19" t="n">
         <v>20</v>
       </c>
-      <c r="E3" s="20" t="n">
-        <v>60.66</v>
-      </c>
-      <c r="F3" s="20" t="n">
-        <v>65.73</v>
-      </c>
-      <c r="G3" s="20" t="n">
-        <v>68.13</v>
-      </c>
-      <c r="H3" s="20" t="n">
-        <v>68.94</v>
-      </c>
-      <c r="I3" s="20" t="n">
-        <v>72.88</v>
-      </c>
-      <c r="J3" s="20" t="n">
-        <v>307.39</v>
-      </c>
-      <c r="K3" s="20" t="n">
-        <v>65.97</v>
-      </c>
-      <c r="L3" s="20" t="n">
-        <v>35</v>
+      <c r="E3" s="19" t="n">
+        <v>61.61</v>
+      </c>
+      <c r="F3" s="19" t="n">
+        <v>65.81999999999999</v>
+      </c>
+      <c r="G3" s="19" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="H3" s="19" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="I3" s="19" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="J3" s="19" t="n">
+        <v>308.44</v>
+      </c>
+      <c r="K3" s="19" t="n">
+        <v>61.69</v>
+      </c>
+      <c r="L3" s="19" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="21" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>G3</t>
         </is>
       </c>
-      <c r="B4" s="21" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>تشاركي+مفتوح</t>
         </is>
       </c>
-      <c r="C4" s="21" t="n">
+      <c r="C4" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="D4" s="21" t="n">
+      <c r="D4" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="E4" s="21" t="n">
-        <v>76.7</v>
-      </c>
-      <c r="F4" s="21" t="n">
-        <v>80.40000000000001</v>
-      </c>
-      <c r="G4" s="21" t="n">
-        <v>82.22</v>
-      </c>
-      <c r="H4" s="21" t="n">
-        <v>79.36</v>
-      </c>
-      <c r="I4" s="21" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="J4" s="21" t="n">
-        <v>364.17</v>
-      </c>
-      <c r="K4" s="21" t="n">
+      <c r="E4" s="20" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="F4" s="20" t="n">
         <v>80.58</v>
       </c>
-      <c r="L4" s="21" t="n">
+      <c r="G4" s="20" t="n">
+        <v>67.23</v>
+      </c>
+      <c r="H4" s="20" t="n">
+        <v>64.83</v>
+      </c>
+      <c r="I4" s="20" t="n">
+        <v>69.95</v>
+      </c>
+      <c r="J4" s="20" t="n">
+        <v>358.4</v>
+      </c>
+      <c r="K4" s="20" t="n">
+        <v>71.67</v>
+      </c>
+      <c r="L4" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="21" t="inlineStr">
         <is>
           <t>G4</t>
         </is>
       </c>
-      <c r="B5" s="22" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>تشاركي+محدد</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="E5" s="22" t="n">
-        <v>58.53</v>
-      </c>
-      <c r="F5" s="22" t="n">
-        <v>62.9</v>
-      </c>
-      <c r="G5" s="22" t="n">
-        <v>78.73999999999999</v>
-      </c>
-      <c r="H5" s="22" t="n">
-        <v>70.44</v>
-      </c>
-      <c r="I5" s="22" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="J5" s="22" t="n">
-        <v>305</v>
-      </c>
-      <c r="K5" s="22" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="L5" s="22" t="n">
-        <v>28</v>
+      <c r="E5" s="21" t="n">
+        <v>64.84999999999999</v>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>74.02</v>
+      </c>
+      <c r="G5" s="21" t="n">
+        <v>59.15</v>
+      </c>
+      <c r="H5" s="21" t="n">
+        <v>55.15</v>
+      </c>
+      <c r="I5" s="21" t="n">
+        <v>62.52</v>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>315.68</v>
+      </c>
+      <c r="K5" s="21" t="n">
+        <v>63.13</v>
+      </c>
+      <c r="L5" s="21" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
